--- a/data/trans_dic/KIDMED_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,89; 74,93</t>
+          <t>50,64; 72,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,78; 70,79</t>
+          <t>55,43; 76,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54,79; 70,29</t>
+          <t>57,11; 72,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,4; 76,67</t>
+          <t>62,87; 75,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,56; 74,79</t>
+          <t>63,88; 75,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,05; 74,44</t>
+          <t>65,56; 73,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,19; 69,21</t>
+          <t>60,58; 72,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,35; 73,0</t>
+          <t>58,56; 70,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,09; 69,22</t>
+          <t>61,98; 70,55</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 59,35</t>
+          <t>52,28; 64,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,85; 62,43</t>
+          <t>52,57; 63,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,4; 59,35</t>
+          <t>53,94; 63,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,51; 64,56</t>
+          <t>59,91; 67,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,54; 66,47</t>
+          <t>60,58; 66,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,0; 64,34</t>
+          <t>61,22; 66,18</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>23188</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>51742</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25058; 34837</t>
+          <t>18956; 26963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21638; 32055</t>
+          <t>23659; 32545</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50289; 64512</t>
+          <t>45754; 57695</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>112918</t>
+          <t>108827</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>125906</t>
+          <t>102538</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238825</t>
+          <t>211364</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>102588; 122141</t>
+          <t>98736; 118566</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>115655; 136095</t>
+          <t>92953; 110547</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225414; 254027</t>
+          <t>198361; 223585</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>108366</t>
+          <t>134851</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>142000</t>
+          <t>113870</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250366</t>
+          <t>248721</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95526; 119783</t>
+          <t>121246; 145830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128230; 155117</t>
+          <t>102296; 123860</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231676; 266890</t>
+          <t>232290; 264429</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>197</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>142245</t>
+          <t>172157</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>171288</t>
+          <t>148678</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313534</t>
+          <t>320835</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96827; 162781</t>
+          <t>152772; 189857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145940; 190414</t>
+          <t>134224; 162881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>262973; 343805</t>
+          <t>295345; 345746</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>585</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>394014</t>
+          <t>439023</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>342979; 421661</t>
+          <t>411473; 463185</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>435981; 495052</t>
+          <t>374528; 412911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>796725; 899449</t>
+          <t>798965; 863679</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/KIDMED_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen una alta adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>61,94%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>66,9%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>50,64; 72,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55,43; 76,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57,11; 72,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>69,3%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>70,46%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,87; 75,5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>63,88; 75,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>65,56; 73,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>65,19%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>60,58; 72,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58,56; 70,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>61,98; 70,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>58,23%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>52,28; 64,97</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>52,57; 63,79</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53,94; 63,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>63,67%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>59,91; 67,44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>60,58; 66,79</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>61,22; 66,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.619432534885573</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6690000933671492</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6458390380793434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>23188</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28554</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51742</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5063806856246115</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5543115312130324</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5710958513871279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18956; 26963</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>23659; 32545</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45754; 57695</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7202564937735901</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7625130059037636</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7201456615245397</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.692977962852127</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7046383725388841</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6985860975383948</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>108827</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>102538</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>211364</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.6287253679390999</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.6387718994135854</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6556074239522698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>98736; 118566</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>92953; 110547</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>198361; 223585</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7549956952263538</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7596802483758924</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.738978861290516</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.673828835956912</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6519099237159538</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.6636136660779198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>134851</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>113870</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>248721</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.6058460867111249</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5856464853283797</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.61977411021287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>121246; 145830</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>102296; 123860</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>232290; 264429</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7286898743731878</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.7091027504006379</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7055230620284434</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5891325539216159</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5822816083352377</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5859378220767336</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>172157</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>148678</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>320835</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5227975531156529</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5256746502731845</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.539385589636557</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>152772; 189857</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>134224; 162881</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>295345; 345746</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.649704204209499</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.637905915481947</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6314332108336489</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.639206958141206</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.6367429309881053</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6380397214334881</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>439023</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>393640</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>832662</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5990956357256126</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.6058277462766886</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.6122188019529697</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>411473; 463185</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>374528; 412911</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>798965; 863679</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.674386325971589</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6679161366000013</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6618076500263844</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen una alta adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>23188</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>28554</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>51742</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>18956</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>23659</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>26963</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>32545</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>57695</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>108827</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>102538</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>211364</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>98736</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>92953</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>198361</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>118566</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>110547</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>223585</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>134851</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>113870</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>248721</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>121246</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>102296</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>232290</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>145830</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>123860</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>264429</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>172157</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>148678</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>320835</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>152772</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>134224</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>295345</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>189857</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>162881</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>345746</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>613</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>585</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>439023</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>393640</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>832662</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>411473</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>374528</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>798965</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>463185</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>412911</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>863679</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>